--- a/assets/libreoffice_calc_njc/30f6d4dc-f47d-4fb7-8309-8f2d3a2c9cd5/EmpComprehensive_L3_02.xlsx
+++ b/assets/libreoffice_calc_njc/30f6d4dc-f47d-4fb7-8309-8f2d3a2c9cd5/EmpComprehensive_L3_02.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -157,15 +157,28 @@
   </si>
   <si>
     <t xml:space="preserve">Total Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Rodriguez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarah Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emily Foster</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -241,7 +254,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -254,6 +267,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -263,6 +280,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF3D3D3D"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -272,7 +306,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -707,7 +741,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -726,68 +760,68 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>96800</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="3" t="n">
         <v>4.38</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>484000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>75000</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="3" t="n">
         <v>4.1</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>150000</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>86000</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="3" t="n">
         <v>3.75</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>344000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>74000</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="3" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -808,9 +842,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>1</v>
       </c>
@@ -824,7 +858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>15</v>
       </c>
@@ -835,63 +869,63 @@
         <v>125000</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>115000</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>110000</v>
+        <v>105000</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="0" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="0" t="n">
         <v>95000</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D6" s="0" t="n">
         <v>4.5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/assets/libreoffice_calc_njc/30f6d4dc-f47d-4fb7-8309-8f2d3a2c9cd5/EmpComprehensive_L3_02.xlsx
+++ b/assets/libreoffice_calc_njc/30f6d4dc-f47d-4fb7-8309-8f2d3a2c9cd5/EmpComprehensive_L3_02.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -157,18 +157,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total Salary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Rodriguez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sarah Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emily Foster</t>
   </si>
 </sst>
 </file>
@@ -180,7 +168,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -202,14 +190,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -259,7 +239,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -741,7 +721,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -842,7 +822,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -874,58 +854,58 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>115000</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>105000</v>
+        <v>110000</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>98000</v>
+        <v>95000</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>95000</v>
+        <v>90000</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/assets/libreoffice_calc_njc/30f6d4dc-f47d-4fb7-8309-8f2d3a2c9cd5/EmpComprehensive_L3_02.xlsx
+++ b/assets/libreoffice_calc_njc/30f6d4dc-f47d-4fb7-8309-8f2d3a2c9cd5/EmpComprehensive_L3_02.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="50">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -157,6 +157,21 @@
   </si>
   <si>
     <t xml:space="preserve">Total Salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DepartmentSalary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iris ChenEngineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarah Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarah WilliamsEngineering</t>
   </si>
 </sst>
 </file>
@@ -168,7 +183,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -190,6 +205,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,12 +257,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -249,6 +272,14 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -314,7 +345,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>1001</v>
       </c>
@@ -337,10 +368,11 @@
         <v>4.5</v>
       </c>
       <c r="H2" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E2,$E$2:$E$16,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
         <v>1003</v>
       </c>
@@ -363,10 +395,11 @@
         <v>4.8</v>
       </c>
       <c r="H3" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E3,$E$2:$E$16,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
         <v>1005</v>
       </c>
@@ -389,10 +422,11 @@
         <v>4</v>
       </c>
       <c r="H4" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E4,$E$2:$E$16,0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
         <v>1009</v>
       </c>
@@ -415,10 +449,11 @@
         <v>4.9</v>
       </c>
       <c r="H5" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E5,$E$2:$E$16,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
         <v>1013</v>
       </c>
@@ -441,10 +476,11 @@
         <v>3.7</v>
       </c>
       <c r="H6" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E6,$E$2:$E$16,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
         <v>1008</v>
       </c>
@@ -467,10 +503,11 @@
         <v>3.9</v>
       </c>
       <c r="H7" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E7,$E$2:$E$16,0)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
         <v>1012</v>
       </c>
@@ -493,10 +530,11 @@
         <v>4.3</v>
       </c>
       <c r="H8" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E8,$E$2:$E$16,0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
         <v>1002</v>
       </c>
@@ -519,10 +557,11 @@
         <v>3.8</v>
       </c>
       <c r="H9" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E9,$E$2:$E$16,0)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
         <v>1006</v>
       </c>
@@ -545,10 +584,11 @@
         <v>3.5</v>
       </c>
       <c r="H10" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E10,$E$2:$E$16,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
         <v>1010</v>
       </c>
@@ -571,10 +611,11 @@
         <v>4.1</v>
       </c>
       <c r="H11" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E11,$E$2:$E$16,0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
         <v>1015</v>
       </c>
@@ -597,10 +638,11 @@
         <v>3.6</v>
       </c>
       <c r="H12" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E12,$E$2:$E$16,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
         <v>1004</v>
       </c>
@@ -623,10 +665,11 @@
         <v>3.2</v>
       </c>
       <c r="H13" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E13,$E$2:$E$16,0)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
         <v>1007</v>
       </c>
@@ -649,10 +692,11 @@
         <v>4.2</v>
       </c>
       <c r="H14" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E14,$E$2:$E$16,0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
         <v>1011</v>
       </c>
@@ -675,10 +719,11 @@
         <v>3</v>
       </c>
       <c r="H15" s="0" t="n">
+        <f aca="false">_xlfn.RANK.EQ(E15,$E$2:$E$16,0)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
         <v>1014</v>
       </c>
@@ -721,7 +766,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -821,21 +866,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -851,61 +899,74 @@
       <c r="D2" s="0" t="n">
         <v>4.8</v>
       </c>
+      <c r="H2" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>25</v>
+      <c r="A3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>115000</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <f aca="false">RANK(C3,$C$2:$C$6,0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>110000</v>
+        <v>98000</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>95000</v>
+        <v>105000</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90000</v>
+        <v>95000</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
